--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4415,32 +4415,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127735588</v>
+        <v>127735584</v>
       </c>
       <c r="B35" t="n">
-        <v>92640</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>967</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>405652</v>
+        <v>405724</v>
       </c>
       <c r="R35" t="n">
-        <v>6855684</v>
+        <v>6855697</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4521,32 +4521,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127735584</v>
+        <v>127735588</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>92640</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>967</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405724</v>
+        <v>405652</v>
       </c>
       <c r="R36" t="n">
-        <v>6855697</v>
+        <v>6855684</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -3888,7 +3888,7 @@
         <v>127735592</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127735589</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127735586</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>127735547</v>
       </c>
       <c r="B33" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>127735548</v>
       </c>
       <c r="B34" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>127735588</v>
       </c>
       <c r="B36" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>127735587</v>
       </c>
       <c r="B37" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>127735593</v>
       </c>
       <c r="B38" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>127735549</v>
       </c>
       <c r="B39" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -3888,7 +3888,7 @@
         <v>127735592</v>
       </c>
       <c r="B30" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127735589</v>
       </c>
       <c r="B31" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127735586</v>
       </c>
       <c r="B32" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>127735547</v>
       </c>
       <c r="B33" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>127735548</v>
       </c>
       <c r="B34" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,32 +4415,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127735584</v>
+        <v>127735588</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>92642</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>967</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>405724</v>
+        <v>405652</v>
       </c>
       <c r="R35" t="n">
-        <v>6855697</v>
+        <v>6855684</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4521,32 +4521,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127735588</v>
+        <v>127735584</v>
       </c>
       <c r="B36" t="n">
-        <v>92641</v>
+        <v>79124</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>967</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405652</v>
+        <v>405724</v>
       </c>
       <c r="R36" t="n">
-        <v>6855684</v>
+        <v>6855697</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4630,7 +4630,7 @@
         <v>127735587</v>
       </c>
       <c r="B37" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>127735593</v>
       </c>
       <c r="B38" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>127735549</v>
       </c>
       <c r="B39" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4415,32 +4415,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127735588</v>
+        <v>127735584</v>
       </c>
       <c r="B35" t="n">
-        <v>92642</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>967</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>405652</v>
+        <v>405724</v>
       </c>
       <c r="R35" t="n">
-        <v>6855684</v>
+        <v>6855697</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4521,32 +4521,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127735584</v>
+        <v>127735588</v>
       </c>
       <c r="B36" t="n">
-        <v>79124</v>
+        <v>92642</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>967</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>405724</v>
+        <v>405652</v>
       </c>
       <c r="R36" t="n">
-        <v>6855697</v>
+        <v>6855684</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -3888,7 +3888,7 @@
         <v>127735592</v>
       </c>
       <c r="B30" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127735589</v>
       </c>
       <c r="B31" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127735586</v>
       </c>
       <c r="B32" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>127735547</v>
       </c>
       <c r="B33" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>127735548</v>
       </c>
       <c r="B34" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>127735584</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79127</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>127735588</v>
       </c>
       <c r="B36" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>127735587</v>
       </c>
       <c r="B37" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>127735593</v>
       </c>
       <c r="B38" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>127735549</v>
       </c>
       <c r="B39" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -3888,7 +3888,7 @@
         <v>127735592</v>
       </c>
       <c r="B30" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>127735589</v>
       </c>
       <c r="B31" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>127735586</v>
       </c>
       <c r="B32" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>127735547</v>
       </c>
       <c r="B33" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>127735548</v>
       </c>
       <c r="B34" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>127735584</v>
       </c>
       <c r="B35" t="n">
-        <v>79127</v>
+        <v>79178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         <v>127735588</v>
       </c>
       <c r="B36" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>127735587</v>
       </c>
       <c r="B37" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>127735593</v>
       </c>
       <c r="B38" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>127735549</v>
       </c>
       <c r="B39" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4943,6 +4943,112 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129001304</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92823</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Öjvasseln, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>405825</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6855605</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92841</v>
+        <v>92844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92844</v>
+        <v>92851</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92851</v>
+        <v>92858</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92858</v>
+        <v>92860</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92860</v>
+        <v>92846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92846</v>
+        <v>92847</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -4948,7 +4948,7 @@
         <v>129001304</v>
       </c>
       <c r="B40" t="n">
-        <v>92847</v>
+        <v>92850</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 41753-2025 artfynd.xlsx
+++ b/artfynd/A 41753-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150004</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150008</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150029</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735584</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001304</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606871</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606878</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606880</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606882</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610429</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1920,6 +1980,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610450</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,6 +2087,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610453</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2128,6 +2198,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735548</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2234,6 +2309,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735549</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2340,6 +2420,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735586</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2446,6 +2531,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735587</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2548,6 +2638,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606869</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2650,6 +2745,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606870</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2752,6 +2852,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606879</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2854,6 +2959,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606881</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2956,6 +3066,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610427</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3058,6 +3173,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610428</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3160,6 +3280,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610449</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3266,6 +3391,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150002</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3372,6 +3502,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150006</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3478,6 +3613,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735536</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3584,6 +3724,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735547</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3690,6 +3835,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735588</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3796,6 +3946,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735589</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3902,6 +4057,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735592</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4008,6 +4168,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735593</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4110,6 +4275,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606876</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4212,6 +4382,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606877</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4314,6 +4489,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610446</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4416,6 +4596,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610447</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4522,6 +4707,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150003</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4628,8 +4818,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150005</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>